--- a/data/trans_dic/P6906-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6906-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño</t>
+          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 27,03</t>
+          <t>3,83; 27,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,91; 83,02</t>
+          <t>20,1; 83,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 49,36</t>
+          <t>6,36; 47,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,48</t>
+          <t>0,0; 29,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,48</t>
+          <t>0,0; 49,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 58,25</t>
+          <t>7,73; 51,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,31</t>
+          <t>0,0; 52,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 23,44</t>
+          <t>5,3; 23,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,51; 59,0</t>
+          <t>15,86; 59,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 44,64</t>
+          <t>8,39; 44,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,0</t>
+          <t>0,0; 39,65</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,71; 36,23</t>
+          <t>19,53; 35,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,65; 33,68</t>
+          <t>14,58; 33,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,54; 29,52</t>
+          <t>11,48; 31,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,64; 41,83</t>
+          <t>9,12; 40,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,57; 34,16</t>
+          <t>14,81; 33,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,55; 42,22</t>
+          <t>19,22; 43,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,24; 45,43</t>
+          <t>19,15; 45,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,88; 43,01</t>
+          <t>15,55; 41,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,18; 33,26</t>
+          <t>20,28; 33,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,23; 34,0</t>
+          <t>19,15; 33,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,87; 31,61</t>
+          <t>16,74; 31,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,87; 37,64</t>
+          <t>14,81; 35,89</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,09; 30,6</t>
+          <t>14,84; 30,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,4; 30,97</t>
+          <t>15,01; 31,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,22; 32,71</t>
+          <t>16,14; 33,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,57; 30,1</t>
+          <t>13,28; 30,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,37; 32,4</t>
+          <t>13,01; 32,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,25; 47,81</t>
+          <t>25,15; 48,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,93; 40,09</t>
+          <t>19,44; 39,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,9; 35,57</t>
+          <t>18,93; 36,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,14; 28,52</t>
+          <t>16,5; 28,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,23; 34,86</t>
+          <t>21,56; 34,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,79; 31,75</t>
+          <t>19,5; 32,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,76; 29,79</t>
+          <t>18,01; 30,62</t>
         </is>
       </c>
     </row>
@@ -1142,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,44; 39,44</t>
+          <t>20,98; 44,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,97; 35,48</t>
+          <t>16,88; 36,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,92; 28,99</t>
+          <t>11,48; 28,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,43; 44,35</t>
+          <t>14,13; 42,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 33,84</t>
+          <t>8,46; 34,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,87; 49,92</t>
+          <t>21,65; 47,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 28,83</t>
+          <t>9,96; 28,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,13; 32,86</t>
+          <t>17,47; 32,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,41; 35,79</t>
+          <t>18,85; 35,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,5; 37,84</t>
+          <t>20,9; 37,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,37; 26,06</t>
+          <t>12,88; 25,04</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,11; 28,6</t>
+          <t>8,06; 29,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,3; 41,17</t>
+          <t>14,55; 41,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,04; 49,48</t>
+          <t>19,22; 48,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 26,92</t>
+          <t>8,7; 25,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,37</t>
+          <t>0,0; 43,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 54,65</t>
+          <t>13,1; 53,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,86; 64,28</t>
+          <t>25,16; 64,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,24; 45,63</t>
+          <t>26,63; 45,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,2; 26,39</t>
+          <t>8,43; 27,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,11; 40,01</t>
+          <t>17,66; 40,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,81; 49,39</t>
+          <t>26,65; 49,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,5; 32,37</t>
+          <t>18,98; 32,29</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,02</t>
+          <t>0,0; 74,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,7</t>
+          <t>0,0; 42,26</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,65; 26,87</t>
+          <t>18,99; 26,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,88; 31,09</t>
+          <t>21,21; 30,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,25; 29,12</t>
+          <t>19,04; 28,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,76; 24,42</t>
+          <t>14,51; 24,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,67; 27,49</t>
+          <t>16,43; 28,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,69; 36,26</t>
+          <t>23,59; 36,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,65; 39,62</t>
+          <t>25,81; 38,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,18; 29,99</t>
+          <t>18,01; 29,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,33; 25,67</t>
+          <t>19,12; 25,72</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,65; 31,42</t>
+          <t>23,79; 31,91</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23,8; 31,32</t>
+          <t>23,44; 31,28</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,36; 26,11</t>
+          <t>18,49; 25,62</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño</t>
+          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1815; 12482</t>
+          <t>1767; 12624</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2160; 8574</t>
+          <t>2076; 8647</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1088; 8466</t>
+          <t>1090; 8136</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2171</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5854</t>
+          <t>0; 5891</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5579</t>
+          <t>0; 4994</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>886; 6782</t>
+          <t>900; 5942</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 7874</t>
+          <t>0; 8059</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3353; 15477</t>
+          <t>3502; 15321</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3365; 12026</t>
+          <t>3233; 12185</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3067; 12853</t>
+          <t>2415; 12932</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 9814</t>
+          <t>0; 8458</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28043; 51545</t>
+          <t>27787; 50743</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12643; 29059</t>
+          <t>12583; 28748</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8598; 24078</t>
+          <t>9367; 25614</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5698; 24711</t>
+          <t>5390; 23717</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12344; 27077</t>
+          <t>11744; 26788</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12450; 28331</t>
+          <t>12897; 29335</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8905; 21029</t>
+          <t>8863; 21186</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7934; 21482</t>
+          <t>7769; 20686</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44715; 73695</t>
+          <t>44945; 73657</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29495; 52157</t>
+          <t>29381; 51704</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21577; 40415</t>
+          <t>21405; 40244</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17303; 41038</t>
+          <t>16149; 39132</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19015; 38564</t>
+          <t>18707; 38170</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14223; 30581</t>
+          <t>14823; 31221</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18343; 37006</t>
+          <t>18258; 37479</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12005; 28754</t>
+          <t>12688; 29132</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8664; 22696</t>
+          <t>9115; 22429</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18341; 34724</t>
+          <t>18266; 35124</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13529; 28646</t>
+          <t>13889; 28312</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14280; 26872</t>
+          <t>14303; 27828</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31644; 55928</t>
+          <t>32358; 54953</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36392; 59747</t>
+          <t>36948; 59524</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36531; 58605</t>
+          <t>36000; 60266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30382; 50967</t>
+          <t>30821; 52388</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17672; 37013</t>
+          <t>17675; 37010</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18195; 35114</t>
+          <t>18680; 39271</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14600; 32441</t>
+          <t>15436; 33062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12941; 31471</t>
+          <t>12465; 31275</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5714; 16424</t>
+          <t>5234; 15839</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3306; 14027</t>
+          <t>3506; 14210</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12830; 28010</t>
+          <t>12150; 26654</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14595; 44673</t>
+          <t>15431; 44252</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25374; 48674</t>
+          <t>25875; 48207</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25326; 46698</t>
+          <t>24591; 46926</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31724; 55823</t>
+          <t>30837; 55823</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35223; 68658</t>
+          <t>33933; 65982</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3720; 13122</t>
+          <t>3700; 13509</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5982; 17223</t>
+          <t>6085; 17238</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8988; 22190</t>
+          <t>8620; 21788</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5959; 18156</t>
+          <t>5866; 17111</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6033</t>
+          <t>0; 5984</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3214; 12892</t>
+          <t>3090; 12705</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7657; 19796</t>
+          <t>7748; 19781</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14563; 25329</t>
+          <t>14781; 25102</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4905; 15780</t>
+          <t>5043; 16735</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11851; 26175</t>
+          <t>11556; 26319</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20280; 37365</t>
+          <t>20160; 37668</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23969; 39794</t>
+          <t>23338; 39700</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1070</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 894</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2070</t>
+          <t>0; 2178</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 1070</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 2375</t>
+          <t>0; 2466</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 633</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 633</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>88075; 126925</t>
+          <t>89686; 126337</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>68102; 101429</t>
+          <t>69182; 100999</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>67365; 101921</t>
+          <t>66641; 100637</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>50125; 82915</t>
+          <t>49279; 82439</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>36699; 60513</t>
+          <t>36169; 62153</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>50884; 77900</t>
+          <t>50686; 78378</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57639; 85697</t>
+          <t>55820; 83491</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>64394; 106237</t>
+          <t>63793; 106128</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>133854; 177728</t>
+          <t>132408; 178065</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>127966; 169978</t>
+          <t>128695; 172629</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>134773; 177346</t>
+          <t>132743; 177122</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>127376; 181106</t>
+          <t>128239; 177729</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6906-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6906-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 27,34</t>
+          <t>5,27; 28,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,1; 83,73</t>
+          <t>20,13; 83,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 47,44</t>
+          <t>6,34; 48,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,67</t>
+          <t>0,0; 29,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,66</t>
+          <t>0,0; 49,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 51,03</t>
+          <t>7,74; 58,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,52</t>
+          <t>0,0; 56,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 23,2</t>
+          <t>5,43; 23,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,86; 59,78</t>
+          <t>16,59; 57,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,39; 44,91</t>
+          <t>10,4; 44,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,65</t>
+          <t>0,0; 38,81</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,53; 35,66</t>
+          <t>20,19; 36,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,58; 33,32</t>
+          <t>14,93; 33,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,48; 31,4</t>
+          <t>10,84; 29,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 40,15</t>
+          <t>13,58; 44,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,81; 33,79</t>
+          <t>15,03; 33,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,22; 43,71</t>
+          <t>20,34; 43,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,15; 45,77</t>
+          <t>18,41; 44,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,55; 41,41</t>
+          <t>14,62; 41,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,28; 33,24</t>
+          <t>20,36; 32,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,15; 33,71</t>
+          <t>19,07; 34,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,74; 31,47</t>
+          <t>17,29; 32,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,81; 35,89</t>
+          <t>16,77; 37,22</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,84; 30,29</t>
+          <t>14,92; 29,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,01; 31,61</t>
+          <t>14,57; 31,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,14; 33,13</t>
+          <t>15,76; 32,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,28; 30,49</t>
+          <t>12,81; 28,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,01; 32,02</t>
+          <t>12,91; 32,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,15; 48,36</t>
+          <t>26,0; 49,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,44; 39,62</t>
+          <t>17,74; 39,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,93; 36,83</t>
+          <t>18,51; 34,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,5; 28,03</t>
+          <t>16,51; 28,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,56; 34,73</t>
+          <t>20,79; 35,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,5; 32,65</t>
+          <t>19,19; 32,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,01; 30,62</t>
+          <t>17,09; 29,08</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,91; 33,31</t>
+          <t>15,93; 32,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,98; 44,11</t>
+          <t>21,02; 42,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,88; 36,16</t>
+          <t>16,24; 35,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,48; 28,81</t>
+          <t>13,37; 30,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,13; 42,77</t>
+          <t>15,39; 43,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 34,28</t>
+          <t>8,31; 35,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,65; 47,5</t>
+          <t>23,3; 48,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 28,56</t>
+          <t>20,88; 33,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,47; 32,54</t>
+          <t>18,08; 32,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 35,97</t>
+          <t>18,64; 34,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,9; 37,84</t>
+          <t>21,03; 37,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,88; 25,04</t>
+          <t>19,25; 29,45</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,06; 29,44</t>
+          <t>8,08; 30,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 41,21</t>
+          <t>14,44; 41,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,22; 48,58</t>
+          <t>19,64; 50,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,7; 25,37</t>
+          <t>9,41; 25,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,02</t>
+          <t>0,0; 43,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,1; 53,86</t>
+          <t>12,92; 57,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,16; 64,22</t>
+          <t>26,19; 64,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,63; 45,22</t>
+          <t>28,6; 46,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,43; 27,99</t>
+          <t>8,11; 26,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,66; 40,23</t>
+          <t>18,18; 41,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,65; 49,8</t>
+          <t>26,23; 49,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,98; 32,29</t>
+          <t>20,19; 32,8</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,74</t>
+          <t>0,0; 72,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,26</t>
+          <t>0,0; 37,07</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,99; 26,75</t>
+          <t>18,68; 26,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,21; 30,96</t>
+          <t>21,5; 31,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,04; 28,75</t>
+          <t>19,45; 29,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,51; 24,28</t>
+          <t>15,29; 24,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,43; 28,24</t>
+          <t>16,67; 27,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,59; 36,48</t>
+          <t>23,1; 35,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,81; 38,6</t>
+          <t>26,98; 39,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,01; 29,96</t>
+          <t>23,65; 32,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,12; 25,72</t>
+          <t>19,21; 25,93</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,79; 31,91</t>
+          <t>23,55; 31,38</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23,44; 31,28</t>
+          <t>23,64; 31,07</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,49; 25,62</t>
+          <t>20,75; 27,36</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2820</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1767; 12624</t>
+          <t>2434; 13018</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2076; 8647</t>
+          <t>2079; 8596</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1090; 8136</t>
+          <t>1087; 8346</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5891</t>
+          <t>0; 5865</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4994</t>
+          <t>0; 5016</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>900; 5942</t>
+          <t>901; 6788</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 8059</t>
+          <t>0; 8966</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3502; 15321</t>
+          <t>3584; 15465</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3233; 12185</t>
+          <t>3381; 11764</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2415; 12932</t>
+          <t>2995; 12687</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 8458</t>
+          <t>0; 9748</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>18481</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13138</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26936</t>
+          <t>31619</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27787; 50743</t>
+          <t>28727; 51398</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12583; 28748</t>
+          <t>12886; 28676</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9367; 25614</t>
+          <t>8844; 23819</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5390; 23717</t>
+          <t>9452; 30857</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11744; 26788</t>
+          <t>11914; 26278</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12897; 29335</t>
+          <t>13649; 29087</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8863; 21186</t>
+          <t>8521; 20566</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7769; 20686</t>
+          <t>7530; 21130</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44945; 73657</t>
+          <t>45114; 72121</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29381; 51704</t>
+          <t>29257; 52241</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21405; 40244</t>
+          <t>22109; 41064</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16149; 39132</t>
+          <t>20304; 45069</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>21790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>22516</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40016</t>
+          <t>44306</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18707; 38170</t>
+          <t>18800; 37726</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14823; 31221</t>
+          <t>14393; 30736</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18258; 37479</t>
+          <t>17826; 36387</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12688; 29132</t>
+          <t>14091; 31439</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9115; 22429</t>
+          <t>9041; 22410</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18266; 35124</t>
+          <t>18883; 36135</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13889; 28312</t>
+          <t>12674; 28303</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14303; 27828</t>
+          <t>16033; 29543</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32358; 54953</t>
+          <t>32379; 56269</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36948; 59524</t>
+          <t>35631; 61509</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36000; 60266</t>
+          <t>35413; 59587</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30821; 52388</t>
+          <t>33593; 57169</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>25364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31921</t>
+          <t>34072</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52532</t>
+          <t>59436</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17675; 37010</t>
+          <t>17703; 36083</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18680; 39271</t>
+          <t>18713; 37416</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15436; 33062</t>
+          <t>14844; 32807</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12465; 31275</t>
+          <t>16116; 36486</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5234; 15839</t>
+          <t>5700; 16273</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3506; 14210</t>
+          <t>3444; 14886</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12150; 26654</t>
+          <t>13071; 27297</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15431; 44252</t>
+          <t>26414; 42654</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25875; 48207</t>
+          <t>26779; 48476</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24591; 46926</t>
+          <t>24325; 45597</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30837; 55823</t>
+          <t>31020; 55878</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33933; 65982</t>
+          <t>47550; 72758</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10778</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20131</t>
+          <t>22941</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>34744</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3700; 13509</t>
+          <t>3705; 13887</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6085; 17238</t>
+          <t>6040; 17248</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8620; 21788</t>
+          <t>8807; 22439</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5866; 17111</t>
+          <t>6775; 18648</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5984</t>
+          <t>0; 6008</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3090; 12705</t>
+          <t>3048; 13505</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7748; 19781</t>
+          <t>8065; 19932</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14781; 25102</t>
+          <t>17667; 28950</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5043; 16735</t>
+          <t>4847; 16063</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11556; 26319</t>
+          <t>11894; 27098</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20160; 37668</t>
+          <t>19840; 37167</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23338; 39700</t>
+          <t>27016; 43887</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>569</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>569</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2178</t>
+          <t>0; 2164</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 2466</t>
+          <t>0; 2471</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64442</t>
+          <t>77437</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>89206</t>
+          <t>96056</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>153648</t>
+          <t>173494</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>89686; 126337</t>
+          <t>88246; 126617</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>69182; 100999</t>
+          <t>70136; 102828</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66641; 100637</t>
+          <t>68077; 101494</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>49279; 82439</t>
+          <t>58875; 94842</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>36169; 62153</t>
+          <t>36686; 60996</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>50686; 78378</t>
+          <t>49624; 77038</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>55820; 83491</t>
+          <t>58361; 85372</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>63793; 106128</t>
+          <t>81681; 111908</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>132408; 178065</t>
+          <t>133037; 179563</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>128695; 172629</t>
+          <t>127406; 169802</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>132743; 177122</t>
+          <t>133864; 175950</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>128239; 177729</t>
+          <t>151571; 199855</t>
         </is>
       </c>
     </row>
